--- a/config/2.报表采集系统_配置.xlsx
+++ b/config/2.报表采集系统_配置.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +49,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00225A9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,10 +69,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,13 +444,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>公开表头示例：不含正式规则、机构资料、业务数据或金融表单模板。</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>配置版本</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>操作说明</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>操作步骤见《基础数据审核工具使用说明.docx》（简易版）；高级开关见《…_高级版.docx》</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>本册用途</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>报表采集系统：指标、机构、环比、校验与外部核对规则；由“执行报表规则”流程读取。金额单位和结果行显示选项在本工作簿的“通用设置”工作表中统一设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>指标参照</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>维护指标代码、表单和数据属性，不按指标逐行设置单位。余额、累发先按单位配置换算到输出文件单位，再进行环比、校验和外部核对；换算不做四舍五入。百分数、个数和文字不换算。再维护环比启用、环比策略组和最小变动值；文字指标三项填写“不适用”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>通用设置</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>选择源数据单位、外部文件单位和输出文件单位；仅支持元、万元、亿元。另可分别选择是否隐藏审核说明为“无变动”的环比行、审核说明为“与大集中系统数据一致”的外部核对行；隐藏行仍保留在结果中，可取消隐藏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>机构参照</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>本机构报送名单与报表项目映射；请按本机构实际情况维护，不要照搬示例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>环比策略</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>按“策略组+规则编号”维护环比区间、数据属性、审核级别、分类说明与禁用；每个策略组必须连续、无重叠、无空档，下限/上限留空表示无穷小/无穷大，采用[下限,上限)。上下限统一填写百分数数值且不带%号，例如10%至30%填写10和30；普通数值按相对变动百分数匹配，百分数按百分点差匹配。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>校验规则</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>表达式与“累计不降”规则；“表达式”用 [代码] 取当期、{代码} 取上期，也可写指标名称；结果为“非空/成立”即触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>外部核对规则</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>固定核对大集中数据，不再填写外部系统。左边是报表指标代码的值，右边是外部指标名称对应的值；比较方式支持等于、不等于、大于、大于等于、小于、小于等于。余额、累发先换算到输出文件单位；仅“等于”使用容差，金额容差按输出文件单位填写，其他比较方式容差必须填0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>最小变动值</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>余额、累发的绝对变动门槛按输出文件单位填写；百分数按百分点、个数按原始数量填写。填写0表示关闭第二道门槛。环比必须同时满足区间和最小变动门槛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>级别口径</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>审核级别使用“提示/关注/严重”；未命中或正常记录审核级别为空白。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>配置检查</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>执行报表规则前会自动阻断结构错误、策略组空档/重叠和未唯一匹配；设置页可点“检查配置”只读查看问题，不会自动修改配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>缺失或损坏</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>请在“设置中心 → 常规设置 → 报表采集系统配置”点“重置”：重置前会自动备份当前文件。</t>
         </is>
       </c>
     </row>

--- a/config/2.报表采集系统_配置.xlsx
+++ b/config/2.报表采集系统_配置.xlsx
@@ -155,6 +155,85 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/s2InstitutionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>User</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="A1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：备用机构匹配字段，同时作为审核结果中的机构名称。
+匹配顺序：先按社会信用代码匹配，未命中时再按源数据中的机构名称匹配。源名称优先读取指标20201001，部分文件格式可回退文件名。
+调整范围：代码能稳定匹配时，可调整配置名称作为输出名称；依赖名称匹配时，须与源名称一致。建议保留正式名称。
+表头保持“机构名称”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：机构身份主匹配键，同时输出到审核结果。
+源数据对应：优先读取机构代码指标20201002；缺失时根据文件格式回退文件名中的机构代码或banks格式的工作表名。先按代码匹配机构参照，未命中才按机构名称匹配。
+外部对应：用于查找外部文件“参照表”中的“统一社会信用代码”，再获取对应“报表项目”。
+调整范围：保持准确、稳定，建议以文本保存并保留前导零。通常不应作为展示文字随意修改。
+表头保持“社会信用代码”，兼容“机构代码”，两者不要同时设置。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：将配置的机构类别补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+调整范围：可按管理分类需要填写或调整，也可留空；修改后结果中的机构类别随之变化。
+表头保持“机构类别”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：将配置的承接行补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+调整范围：可按管理归属需要填写或调整，也可留空；修改后结果中的承接行随之变化。
+表头保持“承接行”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：将配置的地区补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+调整范围：可按管理地区需要填写或调整，也可留空；修改后结果中的地区随之变化。
+表头建议保持“地区”，兼容“归属行”；两者不要同时设置。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：外部核对的备用机构行标签，不直接输出到审核结果。
+对应对象：外部文件“集中系统数据”中的机构行标签，应准确对应（按去除首尾空格后的文本匹配，不做模糊匹配）。
+优先级：先用机构代码查外部文件“参照表”的“统一社会信用代码→报表项目”映射；没有该代码映射时，才回退使用本列。只修改本列不一定改变实际取数对象。
+调整范围：跟随外部机构行标签维护；需要回退匹配时不可随意改成展示名称。
+表头保持“报表项目”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：控制是否加载本行机构参照映射，不直接输出。
+填“是”会跳过此行映射；填“否”或留空会加载。兼容1/true/y/yes表示禁用。
+注意：禁用映射不等于排除该机构或停止审核。源文件仍可能被导入，并按源机构代码/名称继续处理；配置中的地区、承接行、机构类别等补充信息可能不再带入。
+表头保持“禁用”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -725,6 +804,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdS2HeaderVml"/>
 </worksheet>
 </file>
 

--- a/config/2.报表采集系统_配置.xlsx
+++ b/config/2.报表采集系统_配置.xlsx
@@ -15,7 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部核对规则" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通用设置" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'校验规则'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'环比策略'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'外部核对规则'!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -155,83 +159,69 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/s2InstitutionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author>User</x:author>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：备用机构匹配字段，同时作为审核结果中的机构名称。
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：备用机构匹配字段，同时作为审核结果中的机构名称。
 匹配顺序：先按社会信用代码匹配，未命中时再按源数据中的机构名称匹配。源名称优先读取指标20201001，部分文件格式可回退文件名。
 调整范围：代码能稳定匹配时，可调整配置名称作为输出名称；依赖名称匹配时，须与源名称一致。建议保留正式名称。
-表头保持“机构名称”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="B1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：机构身份主匹配键，同时输出到审核结果。
+表头保持“机构名称”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：机构身份主匹配键，同时输出到审核结果。
 源数据对应：优先读取机构代码指标20201002；缺失时根据文件格式回退文件名中的机构代码或banks格式的工作表名。先按代码匹配机构参照，未命中才按机构名称匹配。
 外部对应：用于查找外部文件“参照表”中的“统一社会信用代码”，再获取对应“报表项目”。
 调整范围：保持准确、稳定，建议以文本保存并保留前导零。通常不应作为展示文字随意修改。
-表头保持“社会信用代码”，兼容“机构代码”，两者不要同时设置。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="C1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：将配置的机构类别补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+表头保持“社会信用代码”，兼容“机构代码”，两者不要同时设置。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：将配置的机构类别补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
 调整范围：可按管理分类需要填写或调整，也可留空；修改后结果中的机构类别随之变化。
-表头保持“机构类别”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="D1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：将配置的承接行补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+表头保持“机构类别”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：将配置的承接行补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
 调整范围：可按管理归属需要填写或调整，也可留空；修改后结果中的承接行随之变化。
-表头保持“承接行”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="E1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：将配置的地区补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+表头保持“承接行”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：将配置的地区补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
 调整范围：可按管理地区需要填写或调整，也可留空；修改后结果中的地区随之变化。
-表头建议保持“地区”，兼容“归属行”；两者不要同时设置。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="F1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：外部核对的备用机构行标签，不直接输出到审核结果。
+表头建议保持“地区”，兼容“归属行”；两者不要同时设置。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：外部核对的备用机构行标签，不直接输出到审核结果。
 对应对象：外部文件“集中系统数据”中的机构行标签，应准确对应（按去除首尾空格后的文本匹配，不做模糊匹配）。
 优先级：先用机构代码查外部文件“参照表”的“统一社会信用代码→报表项目”映射；没有该代码映射时，才回退使用本列。只修改本列不一定改变实际取数对象。
 调整范围：跟随外部机构行标签维护；需要回退匹配时不可随意改成展示名称。
-表头保持“报表项目”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="G1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：控制是否加载本行机构参照映射，不直接输出。
+表头保持“报表项目”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：控制是否加载本行机构参照映射，不直接输出。
 填“是”会跳过此行映射；填“否”或留空会加载。兼容1/true/y/yes表示禁用。
 注意：禁用映射不等于排除该机构或停止审核。源文件仍可能被导入，并按源机构代码/名称继续处理；配置中的地区、承接行、机构类别等补充信息可能不再带入。
-表头保持“禁用”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
+表头保持“禁用”，可调整列顺序。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -662,7 +652,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>审核级别使用“提示/关注/严重”；未命中或正常记录审核级别为空白。</t>
+          <t>审核级别仅使用“硬性/软性”；旧配置“严重/错误”按硬性读取，“提示/关注/核实”按软性读取。此级别用于结果分类和筛选，不改变规则执行或流程阻断；未命中或正常记录审核级别为空白。配置检查只提示旧值，不会自动修改工作簿。</t>
         </is>
       </c>
     </row>
@@ -804,7 +794,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdS2HeaderVml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -855,6 +845,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="审核级别无效" error="审核级别只能选择硬性或软性。" promptTitle="选择审核级别" prompt="硬性对应旧严重/错误；软性合并旧提示/关注/核实。该级别用于筛选，不改变流程是否阻断。" type="list">
+      <formula1>"硬性,软性"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -911,6 +907,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="审核级别无效" error="审核级别只能选择硬性或软性。" promptTitle="选择审核级别" prompt="硬性对应旧严重/错误；软性合并旧提示/关注/核实。该级别用于筛选，不改变流程是否阻断。" type="list">
+      <formula1>"硬性,软性"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -962,6 +964,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="审核级别无效" error="审核级别只能选择硬性或软性。" promptTitle="选择审核级别" prompt="硬性对应旧严重/错误；软性合并旧提示/关注/核实。该级别用于筛选，不改变流程是否阻断。" type="list">
+      <formula1>"硬性,软性"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
